--- a/backtest_runs/20260410_193731/by_symbol/RUBY/RUBY.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/RUBY/RUBY.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>116695.31</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>124562.21</v>
@@ -1093,7 +1093,7 @@
         <v>-1660.789999999996</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>122901.42</v>
@@ -1139,7 +1139,7 @@
         <v>-6031.290000000011</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>116870.13</v>
@@ -1231,7 +1231,7 @@
         <v>-7954.310000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>116433.08</v>
@@ -1369,7 +1369,7 @@
         <v>-3846.040000000011</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>112587.04</v>
@@ -1415,7 +1415,7 @@
         <v>-349.6399999999925</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>112237.4</v>
